--- a/ilnlp/Example/HC_GC_data.xlsx
+++ b/ilnlp/Example/HC_GC_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\54126\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2188CE06-75E9-4C35-9975-790B53D037EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F97F7551-4A3F-40DD-A451-6A29757A4599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HC_5" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,12 @@
     <sheet name="GC_5" sheetId="4" r:id="rId4"/>
     <sheet name="GC_10" sheetId="5" r:id="rId5"/>
     <sheet name="GC_30" sheetId="6" r:id="rId6"/>
+    <sheet name="choice_HC_5" sheetId="7" r:id="rId7"/>
+    <sheet name="choice_HC_10 " sheetId="8" r:id="rId8"/>
+    <sheet name="choice_HC_30" sheetId="9" r:id="rId9"/>
+    <sheet name="choice_GC_5" sheetId="10" r:id="rId10"/>
+    <sheet name="choice_GC_10" sheetId="11" r:id="rId11"/>
+    <sheet name="choice_GC_30" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="8">
   <si>
     <t>number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -62,6 +68,14 @@
   </si>
   <si>
     <t>|A|</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,48</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110.6·</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -698,6 +712,777 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005CC8AE-306F-4934-B6D6-A63A5502068C}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="14.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2.4500000000000001E-2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>16.7</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="E2" s="1">
+        <v>43.2</v>
+      </c>
+      <c r="F2" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2.69E-2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>18.7</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="E3" s="1">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="F3" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>4.1799999999999997E-2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>18.3</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.51</v>
+      </c>
+      <c r="E4" s="1">
+        <v>42.5</v>
+      </c>
+      <c r="F4" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>6.6900000000000001E-2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="E5" s="1">
+        <v>50.3</v>
+      </c>
+      <c r="F5" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="E6" s="1">
+        <v>52.8</v>
+      </c>
+      <c r="F6" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="C7" s="1">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="E7" s="1">
+        <v>53.3</v>
+      </c>
+      <c r="F7" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>5.1799999999999999E-2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="E8" s="1">
+        <v>45.2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>5.4699999999999999E-2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.51</v>
+      </c>
+      <c r="E9" s="1">
+        <v>41.7</v>
+      </c>
+      <c r="F9" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="C10" s="1">
+        <v>12.8</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="E10" s="1">
+        <v>61.5</v>
+      </c>
+      <c r="F10" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>6.2399999999999997E-2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="E11" s="1">
+        <v>49.8</v>
+      </c>
+      <c r="F11" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="2">
+        <f>AVERAGE(B2:B11)</f>
+        <v>4.9750000000000003E-2</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" ref="C12:E12" si="0">AVERAGE(C2:C11)</f>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>0.57300000000000006</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
+        <v>48.11</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{156467A9-7A77-44C8-B2C6-096F690DA837}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="16.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.75" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.15579999999999999</v>
+      </c>
+      <c r="C2" s="1">
+        <v>18.7</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="E2" s="1">
+        <v>58.4</v>
+      </c>
+      <c r="F2" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.16239999999999999</v>
+      </c>
+      <c r="C3" s="1">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="E3" s="1">
+        <v>65.2</v>
+      </c>
+      <c r="F3" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.10440000000000001</v>
+      </c>
+      <c r="C4" s="1">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="E4" s="1">
+        <v>60.7</v>
+      </c>
+      <c r="F4" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.1085</v>
+      </c>
+      <c r="C5" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="E5" s="1">
+        <v>57.8</v>
+      </c>
+      <c r="F5" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="C6" s="1">
+        <v>12.6</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="E6" s="1">
+        <v>62.8</v>
+      </c>
+      <c r="F6" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3.4099999999999998E-2</v>
+      </c>
+      <c r="C7" s="1">
+        <v>13</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="E7" s="1">
+        <v>59.7</v>
+      </c>
+      <c r="F7" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>6.25E-2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>17.8</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="E8" s="1">
+        <v>64.2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>6.5600000000000006E-2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="E9" s="1">
+        <v>63.8</v>
+      </c>
+      <c r="F9" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>9.9900000000000003E-2</v>
+      </c>
+      <c r="C10" s="1">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="E10" s="1">
+        <v>67</v>
+      </c>
+      <c r="F10" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="C11" s="1">
+        <v>18</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="E11" s="1">
+        <v>72.599999999999994</v>
+      </c>
+      <c r="F11" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="2">
+        <f>AVERAGE(B2:B11)</f>
+        <v>0.10352000000000001</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" ref="C12:E12" si="0">AVERAGE(C2:C11)</f>
+        <v>16.589999999999996</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>0.72899999999999987</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
+        <v>63.220000000000006</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{053A5656-7417-4A83-9549-743EFA233C6A}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.75" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.18870000000000001</v>
+      </c>
+      <c r="C2" s="1">
+        <v>18.7</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="E2" s="1">
+        <v>83.1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.251</v>
+      </c>
+      <c r="C3" s="1">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E3" s="1">
+        <v>100.6</v>
+      </c>
+      <c r="F3" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="C4" s="1">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1.08</v>
+      </c>
+      <c r="E4" s="1">
+        <v>94.2</v>
+      </c>
+      <c r="F4" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.3483</v>
+      </c>
+      <c r="C5" s="1">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.04</v>
+      </c>
+      <c r="E5" s="1">
+        <v>91</v>
+      </c>
+      <c r="F5" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.1794</v>
+      </c>
+      <c r="C6" s="1">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.26</v>
+      </c>
+      <c r="E6" s="1">
+        <v>101.7</v>
+      </c>
+      <c r="F6" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.39029999999999998</v>
+      </c>
+      <c r="C7" s="1">
+        <v>18.2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1.39</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.17910000000000001</v>
+      </c>
+      <c r="C8" s="1">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1.04</v>
+      </c>
+      <c r="E8" s="1">
+        <v>90.3</v>
+      </c>
+      <c r="F8" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.31380000000000002</v>
+      </c>
+      <c r="C9" s="1">
+        <v>17.7</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.79</v>
+      </c>
+      <c r="E9" s="1">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="F9" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.39079999999999998</v>
+      </c>
+      <c r="C10" s="1">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="E10" s="1">
+        <v>103.4</v>
+      </c>
+      <c r="F10" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.2974</v>
+      </c>
+      <c r="C11" s="1">
+        <v>14.4</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="E11" s="1">
+        <v>97.9</v>
+      </c>
+      <c r="F11" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="2">
+        <f>AVERAGE(B2:B11)</f>
+        <v>0.27718000000000004</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" ref="C12:E12" si="0">AVERAGE(C2:C11)</f>
+        <v>18.46</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0980000000000001</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
+        <v>92.533333333333331</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45848629-A3DE-43B9-B8AA-349FD5BAF303}">
   <dimension ref="A1:F22"/>
@@ -944,7 +1729,7 @@
         <v>4.9859999999999998</v>
       </c>
       <c r="E12" s="2">
-        <f t="shared" ref="D12:F12" si="0">AVERAGE(E2:E11)</f>
+        <f t="shared" ref="E12:F12" si="0">AVERAGE(E2:E11)</f>
         <v>184.06</v>
       </c>
       <c r="F12" s="2">
@@ -2000,4 +2785,775 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8090C5E3-FC3C-4175-B982-23358CF31A35}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="C2" s="1">
+        <v>14.4</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="E2" s="1">
+        <v>73</v>
+      </c>
+      <c r="F2" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1.43E-2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>17.8</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="E3" s="1">
+        <v>59.7</v>
+      </c>
+      <c r="F3" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>18.5</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E4" s="1">
+        <v>60.5</v>
+      </c>
+      <c r="F4" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1.2200000000000001E-2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>17.3</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.31</v>
+      </c>
+      <c r="E5" s="1">
+        <v>67</v>
+      </c>
+      <c r="F5" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1.17E-2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>17.7</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="E6" s="1">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="F6" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>16.8</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1.36</v>
+      </c>
+      <c r="E7" s="1">
+        <v>68.8</v>
+      </c>
+      <c r="F7" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1.3299999999999999E-2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>13.2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1.23</v>
+      </c>
+      <c r="E8" s="1">
+        <v>62.3</v>
+      </c>
+      <c r="F8" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>18</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="E9" s="1">
+        <v>61.5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1.46E-2</v>
+      </c>
+      <c r="C10" s="1">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E10" s="1">
+        <v>60.3</v>
+      </c>
+      <c r="F10" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1.2200000000000001E-2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="E11" s="1">
+        <v>74.400000000000006</v>
+      </c>
+      <c r="F11" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="2">
+        <f>AVERAGE(B2:B11)</f>
+        <v>1.2630000000000002E-2</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" ref="C12:E12" si="0">AVERAGE(C2:C11)</f>
+        <v>17.05</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>1.2710000000000001</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
+        <v>65.16</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7AA50A4-2294-4313-8E8E-CCF8BD7AF719}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>6.2399999999999997E-2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>13.6</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="E2" s="1">
+        <v>97</v>
+      </c>
+      <c r="F2" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>18.2</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1.67</v>
+      </c>
+      <c r="E3" s="1">
+        <v>89.9</v>
+      </c>
+      <c r="F3" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>18.3</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="E4" s="1">
+        <v>85.4</v>
+      </c>
+      <c r="F4" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>18.2</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="E5" s="1">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="F5" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>18.3</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="E6" s="1">
+        <v>61.4</v>
+      </c>
+      <c r="F6" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3.1399999999999997E-2</v>
+      </c>
+      <c r="C7" s="1">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="E7" s="1">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="F7" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>4.4699999999999997E-2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>18.3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="1">
+        <v>83.6</v>
+      </c>
+      <c r="F8" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2.76E-2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>18.3</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="E9" s="1">
+        <v>87.4</v>
+      </c>
+      <c r="F9" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>4.02E-2</v>
+      </c>
+      <c r="C10" s="1">
+        <v>17.7</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="E10" s="1">
+        <v>93.9</v>
+      </c>
+      <c r="F10" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>18.5</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="E11" s="1">
+        <v>97.9</v>
+      </c>
+      <c r="F11" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="2">
+        <f>AVERAGE(B2:B11)</f>
+        <v>3.5590000000000004E-2</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" ref="C12:E12" si="0">AVERAGE(C2:C11)</f>
+        <v>17.739999999999998</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>1.617777777777778</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
+        <v>84.199999999999989</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EAE5157-CF1E-48E1-B9A1-353FAFABA780}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="16.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.1918</v>
+      </c>
+      <c r="C2" s="1">
+        <v>13.4</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="E2" s="1">
+        <v>88.2</v>
+      </c>
+      <c r="F2" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>6.6299999999999998E-2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>14.9</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2.54</v>
+      </c>
+      <c r="E3" s="1">
+        <v>102.9</v>
+      </c>
+      <c r="F3" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.17430000000000001</v>
+      </c>
+      <c r="C4" s="1">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1">
+        <v>136.1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="E5" s="1">
+        <v>93.6</v>
+      </c>
+      <c r="F5" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>6.6400000000000001E-2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.67</v>
+      </c>
+      <c r="E6" s="1">
+        <v>96.4</v>
+      </c>
+      <c r="F6" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.15429999999999999</v>
+      </c>
+      <c r="C7" s="1">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1.99</v>
+      </c>
+      <c r="E7" s="1">
+        <v>138.6</v>
+      </c>
+      <c r="F7" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.17749999999999999</v>
+      </c>
+      <c r="C8" s="1">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E8" s="1">
+        <v>143</v>
+      </c>
+      <c r="F8" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.11360000000000001</v>
+      </c>
+      <c r="C9" s="1">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="E9" s="1">
+        <v>126.8</v>
+      </c>
+      <c r="F9" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.16880000000000001</v>
+      </c>
+      <c r="C10" s="1">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="E10" s="1">
+        <v>133.4</v>
+      </c>
+      <c r="F10" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.10920000000000001</v>
+      </c>
+      <c r="C11" s="1">
+        <v>19.5</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1.79</v>
+      </c>
+      <c r="E11" s="1">
+        <v>113.1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="2">
+        <f>AVERAGE(B2:B11)</f>
+        <v>0.12529999999999999</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" ref="C12:E12" si="0">AVERAGE(C2:C11)</f>
+        <v>17.149999999999999</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>1.9240000000000002</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
+        <v>117.21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>